--- a/VerveStacks_GBR_grids_kan10/SuppXLS/Scen_TSParameters_ts_60c.xlsx
+++ b/VerveStacks_GBR_grids_kan10/SuppXLS/Scen_TSParameters_ts_60c.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_GBR_grids_kan10\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E5B48BD6-43FA-425B-8E49-538685E97850}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E58952E8-62BA-47CA-A463-3CF3C325C10F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -903,13 +903,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S01aH03,S05aH02,S05aH03,S05aH06,S03aH02,S01aH04,S01aH07,S02aH07,S04aH02,S02aH02,S06aH06,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S06aH05,S02aH04,S02aH05,S06aH07,S01aH06,S02aH03,S05aH07,S05aH08,S04aH05,S04aH08,S03aH04,S02aH06,S03aH05,S03aH08,S04aH07,S05aH05,S06aH04,S06aH08,S04aH03,S04aH06,S05aH04,S06aH02,S06aH03,S03aH03,S01aH02,S04aH04</t>
+    <t>S03aH03,S01aH04,S01aH07,S02aH07,S01aH03,S05aH02,S05aH03,S05aH06,S02aH04,S02aH05,S06aH07,S03aH04,S01aH02,S04aH04,S02aH06,S03aH05,S03aH08,S04aH07,S05aH05,S06aH04,S06aH08,S04aH03,S04aH05,S04aH08,S02aH02,S06aH06,S04aH06,S05aH04,S06aH02,S06aH03,S04aH02,S03aH02,S01aH06,S02aH03,S05aH07,S05aH08,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S06aH05</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S04aH02,S01aH09,S01aH10,S03aH02,S03aH01,S01aH02,S05aH10,S03aH08,S03aH10,S06aH08,S01aH01,S04aH01,S06aH02,S04aH08,S06aH01,S05aH08,S02aH09,S04aH09,S05aH01,S03aH09,S05aH09,S02aH01,S02aH10,S05aH02,S06aH09,S02aH02,S04aH10,S06aH10,S01aH08,S02aH08</t>
+    <t>S02aH02,S04aH10,S06aH10,S01aH09,S03aH08,S03aH10,S06aH08,S02aH09,S04aH09,S05aH01,S01aH08,S02aH08,S03aH09,S05aH09,S02aH01,S02aH10,S05aH02,S05aH08,S03aH01,S06aH09,S01aH10,S03aH02,S04aH02,S01aH01,S04aH01,S06aH02,S04aH08,S06aH01,S01aH02,S05aH10</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>S04aH02,S01aH09,S01aH10,S03aH02,S03aH01,S01aH02,S05aH10,S03aH08,S03aH10,S06aH08,S01aH01,S04aH01,S06aH02,S04aH08,S06aH01,S05aH08,S02aH09,S04aH09,S05aH01,S03aH09,S05aH09,S02aH01,S02aH10,S05aH02,S06aH09,S02aH02,S04aH10,S06aH10,S01aH08,S02aH08</v>
+        <v>S02aH02,S04aH10,S06aH10,S01aH09,S03aH08,S03aH10,S06aH08,S02aH09,S04aH09,S05aH01,S01aH08,S02aH08,S03aH09,S05aH09,S02aH01,S02aH10,S05aH02,S05aH08,S03aH01,S06aH09,S01aH10,S03aH02,S04aH02,S01aH01,S04aH01,S06aH02,S04aH08,S06aH01,S01aH02,S05aH10</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>S01aH03,S05aH02,S05aH03,S05aH06,S03aH02,S01aH04,S01aH07,S02aH07,S04aH02,S02aH02,S06aH06,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S06aH05,S02aH04,S02aH05,S06aH07,S01aH06,S02aH03,S05aH07,S05aH08,S04aH05,S04aH08,S03aH04,S02aH06,S03aH05,S03aH08,S04aH07,S05aH05,S06aH04,S06aH08,S04aH03,S04aH06,S05aH04,S06aH02,S06aH03,S03aH03,S01aH02,S04aH04</v>
+        <v>S03aH03,S01aH04,S01aH07,S02aH07,S01aH03,S05aH02,S05aH03,S05aH06,S02aH04,S02aH05,S06aH07,S03aH04,S01aH02,S04aH04,S02aH06,S03aH05,S03aH08,S04aH07,S05aH05,S06aH04,S06aH08,S04aH03,S04aH05,S04aH08,S02aH02,S06aH06,S04aH06,S05aH04,S06aH02,S06aH03,S04aH02,S03aH02,S01aH06,S02aH03,S05aH07,S05aH08,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S06aH05</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -1632,7 +1632,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FBB0C783-D538-4A0E-A3F6-D6B3DFA41699}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B95A7CD-4955-4133-B01D-7848DAF47DBA}">
   <dimension ref="A9:G20"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1776,7 +1776,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DEB04D61-2B47-4BD0-B217-F0950E01520A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B6C4D45-C113-4C31-BAD0-7407066490A3}">
   <dimension ref="B9:O2050"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -60638,7 +60638,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4CAAA0D-38D4-4F7B-8B9C-6F462969FE90}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16FD008A-97BF-44A8-99D3-8D48B4CCF4C7}">
   <dimension ref="B9:IV86"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -91649,7 +91649,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B60AF3A-5F44-4C62-8028-A19BC038AABA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F1BD2F2-00BA-4B68-A08D-20541975500C}">
   <dimension ref="B9:E70"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -92519,7 +92519,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CBEAE61-822D-4895-879F-FC4AD270EECA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7185B67-9A46-405D-A495-69E62364A672}">
   <dimension ref="B9:D130"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -93866,7 +93866,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3CC63F6-66F1-4D16-883C-E546DCA5ED76}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6A48F72-0464-48A2-817D-8DBB9CF1FF3B}">
   <dimension ref="B9:D70"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -94553,7 +94553,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2DF2F73-BD75-4147-9E9D-B74AD662DC7B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71079474-0A8C-414F-8DF1-FD475172F00E}">
   <dimension ref="B9:E184"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
